--- a/Østerbrogade 156.xlsx
+++ b/Østerbrogade 156.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/s203591_dtu_dk/Documents/Virksomhed/Tolderlund/Time-Registrering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{D5024EA8-CA12-4979-A499-BBF41D20E830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B4D686C-6496-4179-9304-B88F53B106F8}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{D5024EA8-CA12-4979-A499-BBF41D20E830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B51F27AD-016E-480C-A6E6-2F8B571F5932}"/>
   <bookViews>
-    <workbookView xWindow="8190" yWindow="3390" windowWidth="27060" windowHeight="15345" xr2:uid="{38E477F2-BF6E-43E2-B308-6D31204D4F28}"/>
+    <workbookView xWindow="19620" yWindow="1665" windowWidth="27060" windowHeight="15345" xr2:uid="{38E477F2-BF6E-43E2-B308-6D31204D4F28}"/>
   </bookViews>
   <sheets>
     <sheet name="Østerbrogade 156" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>dato</t>
   </si>
@@ -143,6 +156,18 @@
   </si>
   <si>
     <t>Sum timer:</t>
+  </si>
+  <si>
+    <t>18:30-20:30</t>
+  </si>
+  <si>
+    <t>Klargøring af spørgsmål til møde, Møde, Noter efter møde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lastkombinationer + Møde kommentar </t>
+  </si>
+  <si>
+    <t>uge 10</t>
   </si>
 </sst>
 </file>
@@ -285,7 +310,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -463,6 +488,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -626,9 +657,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="16" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -685,6 +719,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1004,7 +1042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{969C46C8-46D8-43DF-AD47-30D3AE2670C9}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1083,7 +1121,7 @@
         <v>15</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E23" si="0">C4+D4/60+E3</f>
+        <f t="shared" ref="E4:E33" si="0">C4+D4/60+E3</f>
         <v>10.5</v>
       </c>
       <c r="F4" t="s">
@@ -1489,13 +1527,60 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C27" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>46029</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46081</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D27">
-        <f>MAX(E2:E49)</f>
+      <c r="D24" s="3">
+        <f>MAX(E2:E23)</f>
         <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <f>C25+D25/60+E23</f>
+        <v>55</v>
+      </c>
+      <c r="F25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B26" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="F26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Østerbrogade 156.xlsx
+++ b/Østerbrogade 156.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/s203591_dtu_dk/Documents/Virksomhed/Tolderlund/Time-Registrering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{D5024EA8-CA12-4979-A499-BBF41D20E830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B51F27AD-016E-480C-A6E6-2F8B571F5932}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{D5024EA8-CA12-4979-A499-BBF41D20E830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E3C14B6-51C6-490F-9340-9D32077F4C30}"/>
   <bookViews>
     <workbookView xWindow="19620" yWindow="1665" windowWidth="27060" windowHeight="15345" xr2:uid="{38E477F2-BF6E-43E2-B308-6D31204D4F28}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
   <si>
     <t>dato</t>
   </si>
@@ -167,7 +167,13 @@
     <t xml:space="preserve">lastkombinationer + Møde kommentar </t>
   </si>
   <si>
-    <t>uge 10</t>
+    <t>tidsregistrering system</t>
+  </si>
+  <si>
+    <t>6:45-8:30</t>
+  </si>
+  <si>
+    <t>uge 10:</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1127,7 @@
         <v>15</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E33" si="0">C4+D4/60+E3</f>
+        <f t="shared" ref="E4:E23" si="0">C4+D4/60+E3</f>
         <v>10.5</v>
       </c>
       <c r="F4" t="s">
@@ -1547,40 +1553,64 @@
         <v>46084</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E25">
         <f>C25+D25/60+E23</f>
-        <v>55</v>
+        <v>53.5</v>
       </c>
       <c r="F25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <f>C26+D26/60+E25</f>
+        <v>55.5</v>
+      </c>
+      <c r="F26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>46085</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B27" s="4">
         <v>0.58333333333333337</v>
       </c>
-      <c r="E26">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="E27">
+        <f>C27+D27/60+E26</f>
+        <v>55.5</v>
+      </c>
+      <c r="F27" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Østerbrogade 156.xlsx
+++ b/Østerbrogade 156.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/s203591_dtu_dk/Documents/Virksomhed/Tolderlund/Time-Registrering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="8_{D5024EA8-CA12-4979-A499-BBF41D20E830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E3C14B6-51C6-490F-9340-9D32077F4C30}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{D5024EA8-CA12-4979-A499-BBF41D20E830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA35B8A4-A36C-43EE-AC49-71DEECAB1018}"/>
   <bookViews>
-    <workbookView xWindow="19620" yWindow="1665" windowWidth="27060" windowHeight="15345" xr2:uid="{38E477F2-BF6E-43E2-B308-6D31204D4F28}"/>
+    <workbookView xWindow="-19290" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{38E477F2-BF6E-43E2-B308-6D31204D4F28}"/>
   </bookViews>
   <sheets>
     <sheet name="Østerbrogade 156" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
   <si>
     <t>dato</t>
   </si>
@@ -174,6 +174,27 @@
   </si>
   <si>
     <t>uge 10:</t>
+  </si>
+  <si>
+    <t>8:30-11:30</t>
+  </si>
+  <si>
+    <t>12:30-13:45</t>
+  </si>
+  <si>
+    <t>14:15-16:15</t>
+  </si>
+  <si>
+    <t>lastkombinationer + Møde kommentar + Data analyse</t>
+  </si>
+  <si>
+    <t>16.30-18:00</t>
+  </si>
+  <si>
+    <t>Data Analyse + sammenligning af de 2 FEM modeler</t>
+  </si>
+  <si>
+    <t>07:15-10:30</t>
   </si>
 </sst>
 </file>
@@ -663,12 +684,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="16" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -725,10 +747,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1048,10 +1066,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{969C46C8-46D8-43DF-AD47-30D3AE2670C9}">
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1071,7 +1089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>46029</v>
       </c>
@@ -1092,7 +1110,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>46030</v>
       </c>
@@ -1113,7 +1131,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>46031</v>
       </c>
@@ -1134,7 +1152,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>46034</v>
       </c>
@@ -1155,7 +1173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>46035</v>
       </c>
@@ -1176,7 +1194,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46036</v>
       </c>
@@ -1197,7 +1215,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1218,7 +1236,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>46053</v>
       </c>
@@ -1239,7 +1257,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>46053</v>
       </c>
@@ -1260,7 +1278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>46058</v>
       </c>
@@ -1281,7 +1299,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>46058</v>
       </c>
@@ -1302,7 +1320,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>46058</v>
       </c>
@@ -1323,7 +1341,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>46059</v>
       </c>
@@ -1344,7 +1362,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>46059</v>
       </c>
@@ -1365,7 +1383,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>46063</v>
       </c>
@@ -1386,7 +1404,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>46063</v>
       </c>
@@ -1407,7 +1425,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>46064</v>
       </c>
@@ -1428,7 +1446,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>46073</v>
       </c>
@@ -1449,7 +1467,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -1470,7 +1488,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>46076</v>
       </c>
@@ -1491,7 +1509,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>46076</v>
       </c>
@@ -1512,7 +1530,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>46076</v>
       </c>
@@ -1533,7 +1551,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>46029</v>
       </c>
@@ -1548,7 +1566,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>46084</v>
       </c>
@@ -1569,7 +1587,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>46084</v>
       </c>
@@ -1590,27 +1608,121 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>46085</v>
-      </c>
-      <c r="B27" s="4">
-        <v>0.58333333333333337</v>
+        <v>46086</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
       </c>
       <c r="E27">
         <f>C27+D27/60+E26</f>
-        <v>55.5</v>
+        <v>58.5</v>
       </c>
       <c r="F27" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>45</v>
+      </c>
+      <c r="E28">
+        <f t="shared" ref="E28:E31" si="1">C28+D28/60+E27</f>
+        <v>59.25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="1"/>
+        <v>61.25</v>
+      </c>
+      <c r="F29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>30</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="1"/>
+        <v>62.75</v>
+      </c>
+      <c r="F30" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>15</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+      <c r="F31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>46</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C35" t="s">
         <v>2</v>
+      </c>
+      <c r="D35" s="5">
+        <f>MAX(E25:E32)-$D$24</f>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Østerbrogade 156.xlsx
+++ b/Østerbrogade 156.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/s203591_dtu_dk/Documents/Virksomhed/Tolderlund/Time-Registrering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{D5024EA8-CA12-4979-A499-BBF41D20E830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA35B8A4-A36C-43EE-AC49-71DEECAB1018}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{D5024EA8-CA12-4979-A499-BBF41D20E830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB1C024B-91D6-45B9-967C-E4ACA5CC5001}"/>
   <bookViews>
-    <workbookView xWindow="-19290" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{38E477F2-BF6E-43E2-B308-6D31204D4F28}"/>
+    <workbookView xWindow="19125" yWindow="2070" windowWidth="13185" windowHeight="15345" xr2:uid="{38E477F2-BF6E-43E2-B308-6D31204D4F28}"/>
   </bookViews>
   <sheets>
     <sheet name="Østerbrogade 156" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <t>dato</t>
   </si>
@@ -195,6 +195,27 @@
   </si>
   <si>
     <t>07:15-10:30</t>
+  </si>
+  <si>
+    <t>uge 11:</t>
+  </si>
+  <si>
+    <t>10:45-14:45</t>
+  </si>
+  <si>
+    <t>kontrol + Fix fejl i model 1 og 2</t>
+  </si>
+  <si>
+    <t>kontrol + Fix fejl i model 1 og 2 + Data Analyse + Formidling</t>
+  </si>
+  <si>
+    <t>17:00-19:15</t>
+  </si>
+  <si>
+    <t>8:00-10:00</t>
+  </si>
+  <si>
+    <t>implementer kommentar fra patrik start fix cladding</t>
   </si>
 </sst>
 </file>
@@ -690,51 +711,51 @@
     <xf numFmtId="16" fontId="16" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="20 % - Farve1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20 % - Farve2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20 % - Farve3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20 % - Farve4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20 % - Farve5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20 % - Farve6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40 % - Farve1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40 % - Farve2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40 % - Farve3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40 % - Farve4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40 % - Farve5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40 % - Farve6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60 % - Farve1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60 % - Farve2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60 % - Farve3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60 % - Farve4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60 % - Farve5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60 % - Farve6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Advarselstekst" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Bemærk!" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Beregning" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Farve1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Farve2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Farve3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Farve4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Farve5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Farve6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Forklarende tekst" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="God" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Kontrollér celle" xfId="13" builtinId="23" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Overskrift 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Overskrift 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Overskrift 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Overskrift 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Sammenkædet celle" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Titel" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Ugyldig" xfId="7" builtinId="27" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -749,8 +770,12 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1066,10 +1091,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{969C46C8-46D8-43DF-AD47-30D3AE2670C9}">
-  <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1089,7 +1114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46029</v>
       </c>
@@ -1110,7 +1135,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46030</v>
       </c>
@@ -1131,7 +1156,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46031</v>
       </c>
@@ -1152,7 +1177,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46034</v>
       </c>
@@ -1173,7 +1198,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46035</v>
       </c>
@@ -1194,7 +1219,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46036</v>
       </c>
@@ -1215,7 +1240,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1236,7 +1261,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46053</v>
       </c>
@@ -1257,7 +1282,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46053</v>
       </c>
@@ -1278,7 +1303,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46058</v>
       </c>
@@ -1299,7 +1324,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46058</v>
       </c>
@@ -1320,7 +1345,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46058</v>
       </c>
@@ -1341,7 +1366,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46059</v>
       </c>
@@ -1362,7 +1387,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46059</v>
       </c>
@@ -1383,7 +1408,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46063</v>
       </c>
@@ -1404,7 +1429,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46063</v>
       </c>
@@ -1425,7 +1450,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46064</v>
       </c>
@@ -1446,7 +1471,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46073</v>
       </c>
@@ -1467,7 +1492,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -1488,7 +1513,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46076</v>
       </c>
@@ -1509,7 +1534,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46076</v>
       </c>
@@ -1530,7 +1555,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46076</v>
       </c>
@@ -1551,7 +1576,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>46029</v>
       </c>
@@ -1566,7 +1591,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46084</v>
       </c>
@@ -1587,7 +1612,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46084</v>
       </c>
@@ -1608,7 +1633,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46086</v>
       </c>
@@ -1629,7 +1654,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46086</v>
       </c>
@@ -1643,14 +1668,14 @@
         <v>45</v>
       </c>
       <c r="E28">
-        <f t="shared" ref="E28:E31" si="1">C28+D28/60+E27</f>
+        <f t="shared" ref="E28:E40" si="1">C28+D28/60+E27</f>
         <v>59.25</v>
       </c>
       <c r="F28" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46086</v>
       </c>
@@ -1671,7 +1696,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46086</v>
       </c>
@@ -1692,7 +1717,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46087</v>
       </c>
@@ -1713,16 +1738,93 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C35" t="s">
+      <c r="B32" s="5"/>
+      <c r="C32" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D32" s="3">
         <f>MAX(E25:E32)-$D$24</f>
         <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B33" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33">
+        <v>4</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <f>C33+D33/60+E31</f>
+        <v>70</v>
+      </c>
+      <c r="F33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>15</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="1"/>
+        <v>72.25</v>
+      </c>
+      <c r="F34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>13</v>
+      </c>
+      <c r="B35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="1"/>
+        <v>74.25</v>
+      </c>
+      <c r="F35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="3">
+        <f>MAX(E33:E40)-$D$24-D32</f>
+        <v>8.25</v>
       </c>
     </row>
   </sheetData>

--- a/Østerbrogade 156.xlsx
+++ b/Østerbrogade 156.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/s203591_dtu_dk/Documents/Virksomhed/Tolderlund/Time-Registrering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="8_{D5024EA8-CA12-4979-A499-BBF41D20E830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB1C024B-91D6-45B9-967C-E4ACA5CC5001}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="8_{D5024EA8-CA12-4979-A499-BBF41D20E830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{943AED32-48D7-4F16-93E0-A774743D6204}"/>
   <bookViews>
-    <workbookView xWindow="19125" yWindow="2070" windowWidth="13185" windowHeight="15345" xr2:uid="{38E477F2-BF6E-43E2-B308-6D31204D4F28}"/>
+    <workbookView xWindow="10290" yWindow="2865" windowWidth="22875" windowHeight="15345" xr2:uid="{38E477F2-BF6E-43E2-B308-6D31204D4F28}"/>
   </bookViews>
   <sheets>
     <sheet name="Østerbrogade 156" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="62">
   <si>
     <t>dato</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>implementer kommentar fra patrik start fix cladding</t>
+  </si>
+  <si>
+    <t>Sum tid:</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{969C46C8-46D8-43DF-AD47-30D3AE2670C9}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1668,7 +1671,7 @@
         <v>45</v>
       </c>
       <c r="E28">
-        <f t="shared" ref="E28:E40" si="1">C28+D28/60+E27</f>
+        <f t="shared" ref="E28:E35" si="1">C28+D28/60+E27</f>
         <v>59.25</v>
       </c>
       <c r="F28" t="s">
@@ -1825,6 +1828,22 @@
       <c r="D36" s="3">
         <f>MAX(E33:E40)-$D$24-D32</f>
         <v>8.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <f>A24</f>
+        <v>46029</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" s="3">
+        <f>D36+D32+D24</f>
+        <v>74.25</v>
       </c>
     </row>
   </sheetData>
